--- a/public/rotations/sample-executive-report.xlsx
+++ b/public/rotations/sample-executive-report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6ff0cde6518eb22/Desktop/AHS Rotations/Shift_analytics/Sample Rotations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6ff0cde6518eb22/Desktop/AHS Rotations/Shift_analytics/public/rotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{94A40F80-70CB-4818-9B7F-F86BAAF2FCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62F14D80-DDDA-4EF7-AF68-473EC599601A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{94A40F80-70CB-4818-9B7F-F86BAAF2FCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85AD2F0-13C4-463A-9D2C-6069E5A56D86}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9219D57D-2CA3-4832-9AC9-F51562264488}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9219D57D-2CA3-4832-9AC9-F51562264488}"/>
   </bookViews>
   <sheets>
     <sheet name="Prepared Report" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
   <si>
-    <t xml:space="preserve"> Rotation Analytics Inc</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Clarity from Complexity</t>
   </si>
   <si>
@@ -448,6 +445,9 @@
   </si>
   <si>
     <t>Sample Article: Regular hours of work shall be deemed to exclude a meal period of not less than thirty (30) minutes to be scheduled by the Employer during each working day on which the Employee works in excess of four (4) hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rotation Analytics</t>
   </si>
 </sst>
 </file>
@@ -1369,10 +1369,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1384,10 +1405,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1408,47 +1447,8 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9388,15 +9388,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB9898E-8227-482E-A4F5-E5873E5690C0}">
   <dimension ref="A1:J149"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.6640625" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
     <col min="2" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="97.77734375" customWidth="1"/>
-    <col min="10" max="10" width="0.6640625" customWidth="1"/>
+    <col min="5" max="5" width="97.7109375" customWidth="1"/>
+    <col min="10" max="10" width="0.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9408,7 +9408,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -9420,13 +9420,13 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -9434,13 +9434,13 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -9448,7 +9448,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -9460,27 +9460,27 @@
       <c r="I5" s="70"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="4"/>
       <c r="D6" s="5"/>
       <c r="E6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="71">
+        <v>46096.672392245368</v>
+      </c>
+      <c r="G6" s="71"/>
+      <c r="H6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="92">
-        <v>46096.672392245368</v>
-      </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="I6" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -9492,23 +9492,23 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="9"/>
       <c r="D8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="93" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="95"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="74"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -9520,7 +9520,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -9528,17 +9528,17 @@
         <v>15</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
+        <v>115</v>
+      </c>
+      <c r="F10" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -9546,23 +9546,23 @@
         <v>10</v>
       </c>
       <c r="E11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="H11" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="I11" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="19" t="s">
-        <v>11</v>
-      </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -9570,7 +9570,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="20">
         <v>5</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -9598,13 +9598,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
       <c r="E14" s="26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -9612,71 +9612,71 @@
       <c r="I14" s="25"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="96" t="s">
+      <c r="C15" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="97"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="97"/>
-      <c r="G15" s="97"/>
-      <c r="H15" s="27" t="s">
+      <c r="I15" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="28" t="s">
-        <v>16</v>
-      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
+      <c r="C16" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="79"/>
       <c r="H16" s="5"/>
       <c r="I16" s="29"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="64">
         <v>1</v>
       </c>
       <c r="D17" s="65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="66"/>
       <c r="F17" s="66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="67">
         <v>38.75</v>
       </c>
       <c r="H17" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="34"/>
       <c r="D18" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F18" s="35"/>
       <c r="G18" s="35"/>
@@ -9684,7 +9684,7 @@
       <c r="I18" s="37"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="34"/>
@@ -9696,53 +9696,53 @@
       <c r="I19" s="37"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="75"/>
+      <c r="C20" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="30">
         <v>2</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" s="63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="34"/>
       <c r="D22" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="35"/>
       <c r="G22" s="35"/>
@@ -9750,7 +9750,7 @@
       <c r="I22" s="37"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="34"/>
@@ -9762,53 +9762,53 @@
       <c r="I23" s="37"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="75"/>
+      <c r="C24" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="82"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="64">
         <v>3</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="66"/>
       <c r="F25" s="66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="67">
         <v>7.75</v>
       </c>
       <c r="H25" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I25" s="63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="92.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="35"/>
@@ -9816,7 +9816,7 @@
       <c r="I26" s="37"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="34"/>
@@ -9828,71 +9828,71 @@
       <c r="I27" s="37"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="34"/>
       <c r="D28" s="35"/>
       <c r="E28" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="G28" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H28" s="35"/>
       <c r="I28" s="37"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="73" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="75"/>
+      <c r="C29" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="82"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="64">
         <v>4</v>
       </c>
       <c r="D30" s="65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" s="66"/>
       <c r="F30" s="66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" s="67">
         <v>30</v>
       </c>
       <c r="H30" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I30" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="34"/>
       <c r="D31" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F31" s="35"/>
       <c r="G31" s="35"/>
@@ -9900,7 +9900,7 @@
       <c r="I31" s="37"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="34"/>
@@ -9912,34 +9912,34 @@
       <c r="I32" s="37"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="34"/>
       <c r="D33" s="35"/>
       <c r="E33" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G33" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H33" s="35"/>
       <c r="I33" s="37"/>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="34"/>
       <c r="D34" s="35"/>
       <c r="E34" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="35" t="s">
         <v>37</v>
-      </c>
-      <c r="F34" s="35" t="s">
-        <v>38</v>
       </c>
       <c r="G34" s="46">
         <v>1</v>
@@ -9948,16 +9948,16 @@
       <c r="I34" s="37"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="34"/>
       <c r="D35" s="35"/>
       <c r="E35" s="47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G35" s="46">
         <v>4</v>
@@ -9966,53 +9966,53 @@
       <c r="I35" s="37"/>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="73" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="74"/>
-      <c r="I36" s="75"/>
+      <c r="C36" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="82"/>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="30">
         <v>5</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G37" s="33">
         <v>15</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I37" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="34"/>
       <c r="D38" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
@@ -10020,7 +10020,7 @@
       <c r="I38" s="37"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="34"/>
@@ -10032,53 +10032,53 @@
       <c r="I39" s="37"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="74"/>
-      <c r="I40" s="75"/>
+      <c r="C40" s="80" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="82"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="64">
         <v>6</v>
       </c>
       <c r="D41" s="65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E41" s="66"/>
       <c r="F41" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G41" s="67" t="s">
-        <v>32</v>
-      </c>
       <c r="H41" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="34"/>
       <c r="D42" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F42" s="35"/>
       <c r="G42" s="35"/>
@@ -10086,7 +10086,7 @@
       <c r="I42" s="37"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="34"/>
@@ -10098,67 +10098,67 @@
       <c r="I43" s="37"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
-      <c r="C44" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="75"/>
+      <c r="C44" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="82"/>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
+      <c r="C45" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="79"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="79"/>
+      <c r="G45" s="79"/>
       <c r="H45" s="5"/>
       <c r="I45" s="29"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="59">
         <v>7</v>
       </c>
       <c r="D46" s="60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E46" s="61"/>
       <c r="F46" s="61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G46" s="62">
         <v>56</v>
       </c>
       <c r="H46" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I46" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="34"/>
       <c r="D47" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F47" s="35"/>
       <c r="G47" s="35"/>
@@ -10166,7 +10166,7 @@
       <c r="I47" s="37"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="34"/>
@@ -10178,16 +10178,16 @@
       <c r="I48" s="37"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="34"/>
       <c r="D49" s="35"/>
       <c r="E49" s="47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G49" s="46">
         <v>2</v>
@@ -10196,16 +10196,16 @@
       <c r="I49" s="37"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="34"/>
       <c r="D50" s="35"/>
       <c r="E50" s="47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G50" s="46">
         <v>5</v>
@@ -10214,75 +10214,75 @@
       <c r="I50" s="37"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="34"/>
       <c r="D51" s="35"/>
       <c r="E51" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G51" s="46" t="s">
         <v>51</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G51" s="46" t="s">
-        <v>52</v>
       </c>
       <c r="H51" s="35"/>
       <c r="I51" s="37"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="34"/>
       <c r="D52" s="35"/>
       <c r="E52" s="47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F52" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G52" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H52" s="35"/>
       <c r="I52" s="37"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="34"/>
       <c r="D53" s="35"/>
       <c r="E53" s="35"/>
-      <c r="F53" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="72"/>
-      <c r="H53" s="72"/>
+      <c r="F53" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G53" s="75"/>
+      <c r="H53" s="75"/>
       <c r="I53" s="37"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="34"/>
       <c r="D54" s="35"/>
       <c r="E54" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="H54" s="91"/>
+        <v>21</v>
+      </c>
+      <c r="G54" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H54" s="86"/>
       <c r="I54" s="37"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="34"/>
@@ -10291,14 +10291,14 @@
       <c r="F55" s="41">
         <v>1</v>
       </c>
-      <c r="G55" s="88" t="s">
-        <v>55</v>
-      </c>
-      <c r="H55" s="89"/>
+      <c r="G55" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" s="84"/>
       <c r="I55" s="37"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="34"/>
@@ -10307,14 +10307,14 @@
       <c r="F56" s="41">
         <v>3</v>
       </c>
-      <c r="G56" s="88" t="s">
-        <v>56</v>
-      </c>
-      <c r="H56" s="89"/>
+      <c r="G56" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="H56" s="84"/>
       <c r="I56" s="37"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="34"/>
@@ -10323,14 +10323,14 @@
       <c r="F57" s="41">
         <v>9</v>
       </c>
-      <c r="G57" s="88" t="s">
-        <v>57</v>
-      </c>
-      <c r="H57" s="89"/>
+      <c r="G57" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="H57" s="84"/>
       <c r="I57" s="37"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="34"/>
@@ -10339,14 +10339,14 @@
       <c r="F58" s="41">
         <v>10</v>
       </c>
-      <c r="G58" s="88" t="s">
-        <v>56</v>
-      </c>
-      <c r="H58" s="89"/>
+      <c r="G58" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="H58" s="84"/>
       <c r="I58" s="37"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="34"/>
@@ -10358,67 +10358,67 @@
       <c r="I59" s="37"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="73" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" s="74"/>
-      <c r="E60" s="74"/>
-      <c r="F60" s="74"/>
-      <c r="G60" s="74"/>
-      <c r="H60" s="74"/>
-      <c r="I60" s="75"/>
+      <c r="C60" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="81"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="81"/>
+      <c r="I60" s="82"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="D61" s="77"/>
-      <c r="E61" s="77"/>
-      <c r="F61" s="77"/>
-      <c r="G61" s="77"/>
+      <c r="C61" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" s="79"/>
+      <c r="E61" s="79"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
       <c r="H61" s="5"/>
       <c r="I61" s="29"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="59">
         <v>8</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E62" s="61"/>
       <c r="F62" s="61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G62" s="62">
         <v>7</v>
       </c>
       <c r="H62" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I62" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="34"/>
       <c r="D63" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E63" s="36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -10426,7 +10426,7 @@
       <c r="I63" s="37"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="34"/>
@@ -10438,34 +10438,34 @@
       <c r="I64" s="37"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="34"/>
       <c r="D65" s="35"/>
       <c r="E65" s="47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F65" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G65" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H65" s="35"/>
       <c r="I65" s="37"/>
       <c r="J65" s="1"/>
     </row>
-    <row r="66" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="34"/>
       <c r="D66" s="35"/>
       <c r="E66" s="47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F66" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G66" s="46">
         <v>7</v>
@@ -10474,16 +10474,16 @@
       <c r="I66" s="37"/>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="34"/>
       <c r="D67" s="35"/>
       <c r="E67" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" s="35" t="s">
         <v>65</v>
-      </c>
-      <c r="F67" s="35" t="s">
-        <v>66</v>
       </c>
       <c r="G67" s="46">
         <v>2</v>
@@ -10492,16 +10492,16 @@
       <c r="I67" s="37"/>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="34"/>
       <c r="D68" s="35"/>
       <c r="E68" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F68" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G68" s="46">
         <v>5</v>
@@ -10510,16 +10510,16 @@
       <c r="I68" s="37"/>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="34"/>
       <c r="D69" s="35"/>
       <c r="E69" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G69" s="46">
         <v>2</v>
@@ -10528,16 +10528,16 @@
       <c r="I69" s="37"/>
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="34"/>
       <c r="D70" s="35"/>
       <c r="E70" s="47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G70" s="46">
         <v>5</v>
@@ -10546,39 +10546,39 @@
       <c r="I70" s="37"/>
       <c r="J70" s="1"/>
     </row>
-    <row r="71" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="34"/>
       <c r="D71" s="35"/>
       <c r="E71" s="35"/>
-      <c r="F71" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="72"/>
+      <c r="F71" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="75"/>
       <c r="H71" s="35"/>
       <c r="I71" s="37"/>
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="34"/>
       <c r="D72" s="35"/>
       <c r="E72" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F72" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G72" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H72" s="26"/>
       <c r="I72" s="37"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="34"/>
@@ -10594,7 +10594,7 @@
       <c r="I73" s="37"/>
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="34"/>
@@ -10606,51 +10606,51 @@
       <c r="I74" s="37"/>
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="1:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="75"/>
+      <c r="C75" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="81"/>
+      <c r="E75" s="81"/>
+      <c r="F75" s="81"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="82"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="64">
         <v>9</v>
       </c>
       <c r="D76" s="65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E76" s="66"/>
       <c r="F76" s="66"/>
       <c r="G76" s="67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I76" s="63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J76" s="1"/>
     </row>
-    <row r="77" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="34"/>
       <c r="D77" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E77" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F77" s="35"/>
       <c r="G77" s="35"/>
@@ -10658,7 +10658,7 @@
       <c r="I77" s="37"/>
       <c r="J77" s="1"/>
     </row>
-    <row r="78" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="34"/>
@@ -10670,16 +10670,16 @@
       <c r="I78" s="37"/>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="34"/>
       <c r="D79" s="35"/>
       <c r="E79" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G79" s="46">
         <v>2</v>
@@ -10688,16 +10688,16 @@
       <c r="I79" s="37"/>
       <c r="J79" s="1"/>
     </row>
-    <row r="80" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="34"/>
       <c r="D80" s="35"/>
       <c r="E80" s="47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F80" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G80" s="46">
         <v>2</v>
@@ -10706,49 +10706,49 @@
       <c r="I80" s="37"/>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
-      <c r="C81" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="74"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="74"/>
-      <c r="I81" s="75"/>
+      <c r="C81" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="D81" s="81"/>
+      <c r="E81" s="81"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="81"/>
+      <c r="I81" s="82"/>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="64">
         <v>10</v>
       </c>
       <c r="D82" s="65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E82" s="66"/>
       <c r="F82" s="66"/>
       <c r="G82" s="67"/>
       <c r="H82" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I82" s="63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="34"/>
       <c r="D83" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E83" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F83" s="35"/>
       <c r="G83" s="35"/>
@@ -10756,7 +10756,7 @@
       <c r="I83" s="37"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="1:10" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" ht="3.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="34"/>
@@ -10768,125 +10768,125 @@
       <c r="I84" s="37"/>
       <c r="J84" s="1"/>
     </row>
-    <row r="85" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="34"/>
       <c r="D85" s="35"/>
       <c r="E85" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F85" s="35" t="s">
         <v>77</v>
-      </c>
-      <c r="F85" s="35" t="s">
-        <v>78</v>
       </c>
       <c r="G85" s="46">
         <v>33.299999999999997</v>
       </c>
-      <c r="H85" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="I85" s="87"/>
+      <c r="H85" s="87" t="s">
+        <v>78</v>
+      </c>
+      <c r="I85" s="88"/>
       <c r="J85" s="1"/>
     </row>
-    <row r="86" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="34"/>
       <c r="D86" s="35"/>
       <c r="E86" s="47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G86" s="46">
         <v>33.299999999999997</v>
       </c>
-      <c r="H86" s="84">
+      <c r="H86" s="89">
         <v>0.5714285714285714</v>
       </c>
-      <c r="I86" s="85"/>
+      <c r="I86" s="90"/>
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="34"/>
       <c r="D87" s="35"/>
       <c r="E87" s="47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G87" s="46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H87" s="35"/>
       <c r="I87" s="37"/>
       <c r="J87" s="1"/>
     </row>
-    <row r="88" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="D88" s="74"/>
-      <c r="E88" s="74"/>
-      <c r="F88" s="74"/>
-      <c r="G88" s="74"/>
-      <c r="H88" s="74"/>
-      <c r="I88" s="75"/>
+      <c r="C88" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="D88" s="81"/>
+      <c r="E88" s="81"/>
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
+      <c r="H88" s="81"/>
+      <c r="I88" s="82"/>
       <c r="J88" s="1"/>
     </row>
-    <row r="89" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="D89" s="77"/>
-      <c r="E89" s="77"/>
-      <c r="F89" s="77"/>
-      <c r="G89" s="77"/>
+      <c r="C89" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" s="79"/>
+      <c r="E89" s="79"/>
+      <c r="F89" s="79"/>
+      <c r="G89" s="79"/>
       <c r="H89" s="5"/>
       <c r="I89" s="29"/>
       <c r="J89" s="1"/>
     </row>
-    <row r="90" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="59">
         <v>11</v>
       </c>
       <c r="D90" s="60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E90" s="61"/>
       <c r="F90" s="61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G90" s="62">
         <v>15.5</v>
       </c>
       <c r="H90" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I90" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J90" s="1"/>
     </row>
-    <row r="91" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="34"/>
       <c r="D91" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E91" s="36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F91" s="35"/>
       <c r="G91" s="35"/>
@@ -10894,7 +10894,7 @@
       <c r="I91" s="37"/>
       <c r="J91" s="1"/>
     </row>
-    <row r="92" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="34"/>
@@ -10906,57 +10906,57 @@
       <c r="I92" s="37"/>
       <c r="J92" s="1"/>
     </row>
-    <row r="93" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="34"/>
       <c r="D93" s="35"/>
       <c r="E93" s="47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F93" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G93" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G93" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H93" s="35"/>
       <c r="I93" s="37"/>
       <c r="J93" s="1"/>
     </row>
-    <row r="94" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="34"/>
       <c r="D94" s="35"/>
       <c r="E94" s="35"/>
-      <c r="F94" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="72"/>
+      <c r="F94" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="75"/>
       <c r="H94" s="25"/>
       <c r="I94" s="37"/>
       <c r="J94" s="1"/>
     </row>
-    <row r="95" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="34"/>
       <c r="D95" s="35"/>
       <c r="E95" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F95" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G95" s="48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H95" s="26"/>
       <c r="I95" s="37"/>
       <c r="J95" s="1"/>
     </row>
-    <row r="96" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="34"/>
@@ -10972,7 +10972,7 @@
       <c r="I96" s="37"/>
       <c r="J96" s="1"/>
     </row>
-    <row r="97" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="34"/>
@@ -10988,7 +10988,7 @@
       <c r="I97" s="37"/>
       <c r="J97" s="1"/>
     </row>
-    <row r="98" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="34"/>
@@ -11004,7 +11004,7 @@
       <c r="I98" s="37"/>
       <c r="J98" s="1"/>
     </row>
-    <row r="99" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="34"/>
@@ -11020,7 +11020,7 @@
       <c r="I99" s="37"/>
       <c r="J99" s="1"/>
     </row>
-    <row r="100" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="34"/>
@@ -11036,7 +11036,7 @@
       <c r="I100" s="37"/>
       <c r="J100" s="1"/>
     </row>
-    <row r="101" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="34"/>
@@ -11048,67 +11048,67 @@
       <c r="I101" s="37"/>
       <c r="J101" s="1"/>
     </row>
-    <row r="102" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
-      <c r="C102" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="D102" s="74"/>
-      <c r="E102" s="74"/>
-      <c r="F102" s="74"/>
-      <c r="G102" s="74"/>
-      <c r="H102" s="74"/>
-      <c r="I102" s="75"/>
+      <c r="C102" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="D102" s="81"/>
+      <c r="E102" s="81"/>
+      <c r="F102" s="81"/>
+      <c r="G102" s="81"/>
+      <c r="H102" s="81"/>
+      <c r="I102" s="82"/>
       <c r="J102" s="1"/>
     </row>
-    <row r="103" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-      <c r="C103" s="76" t="s">
-        <v>88</v>
-      </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="C103" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="D103" s="79"/>
+      <c r="E103" s="79"/>
+      <c r="F103" s="79"/>
+      <c r="G103" s="79"/>
       <c r="H103" s="5"/>
       <c r="I103" s="29"/>
       <c r="J103" s="1"/>
     </row>
-    <row r="104" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="59">
         <v>12</v>
       </c>
       <c r="D104" s="60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E104" s="61"/>
       <c r="F104" s="61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G104" s="62">
         <v>2</v>
       </c>
       <c r="H104" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I104" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J104" s="1"/>
     </row>
-    <row r="105" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="34"/>
       <c r="D105" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E105" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F105" s="35"/>
       <c r="G105" s="35"/>
@@ -11116,7 +11116,7 @@
       <c r="I105" s="37"/>
       <c r="J105" s="1"/>
     </row>
-    <row r="106" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="34"/>
@@ -11128,75 +11128,75 @@
       <c r="I106" s="37"/>
       <c r="J106" s="1"/>
     </row>
-    <row r="107" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="34"/>
       <c r="D107" s="35"/>
       <c r="E107" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F107" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G107" s="46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H107" s="35"/>
       <c r="I107" s="37"/>
       <c r="J107" s="1"/>
     </row>
-    <row r="108" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="34"/>
       <c r="D108" s="35"/>
       <c r="E108" s="47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F108" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G108" s="46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H108" s="35"/>
       <c r="I108" s="37"/>
       <c r="J108" s="1"/>
     </row>
-    <row r="109" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="34"/>
       <c r="D109" s="35"/>
       <c r="E109" s="35"/>
-      <c r="F109" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="G109" s="72"/>
-      <c r="H109" s="72"/>
+      <c r="F109" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G109" s="75"/>
+      <c r="H109" s="75"/>
       <c r="I109" s="37"/>
       <c r="J109" s="1"/>
     </row>
-    <row r="110" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="34"/>
       <c r="D110" s="35"/>
       <c r="E110" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F110" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G110" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="F110" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="G110" s="80" t="s">
-        <v>95</v>
-      </c>
-      <c r="H110" s="81"/>
+      <c r="H110" s="94"/>
       <c r="I110" s="37"/>
       <c r="J110" s="1"/>
     </row>
-    <row r="111" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="34"/>
@@ -11205,14 +11205,14 @@
       <c r="F111" s="41">
         <v>3</v>
       </c>
-      <c r="G111" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="H111" s="83"/>
+      <c r="G111" s="95" t="s">
+        <v>95</v>
+      </c>
+      <c r="H111" s="96"/>
       <c r="I111" s="37"/>
       <c r="J111" s="1"/>
     </row>
-    <row r="112" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="34"/>
@@ -11224,53 +11224,53 @@
       <c r="I112" s="37"/>
       <c r="J112" s="1"/>
     </row>
-    <row r="113" spans="1:10" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
-      <c r="C113" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D113" s="78"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="78"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="79"/>
+      <c r="C113" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D113" s="91"/>
+      <c r="E113" s="91"/>
+      <c r="F113" s="91"/>
+      <c r="G113" s="91"/>
+      <c r="H113" s="91"/>
+      <c r="I113" s="92"/>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="64">
         <v>13</v>
       </c>
       <c r="D114" s="65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E114" s="66"/>
       <c r="F114" s="66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G114" s="67">
         <v>2</v>
       </c>
       <c r="H114" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I114" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J114" s="1"/>
     </row>
-    <row r="115" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="34"/>
       <c r="D115" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E115" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F115" s="35"/>
       <c r="G115" s="35"/>
@@ -11278,7 +11278,7 @@
       <c r="I115" s="37"/>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="34"/>
@@ -11290,16 +11290,16 @@
       <c r="I116" s="37"/>
       <c r="J116" s="1"/>
     </row>
-    <row r="117" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="34"/>
       <c r="D117" s="35"/>
       <c r="E117" s="47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F117" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G117" s="46">
         <v>1</v>
@@ -11308,103 +11308,103 @@
       <c r="I117" s="37"/>
       <c r="J117" s="1"/>
     </row>
-    <row r="118" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="34"/>
       <c r="D118" s="35"/>
       <c r="E118" s="47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F118" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G118" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G118" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H118" s="35"/>
       <c r="I118" s="37"/>
       <c r="J118" s="1"/>
     </row>
-    <row r="119" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="34"/>
       <c r="D119" s="35"/>
       <c r="E119" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F119" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G119" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G119" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H119" s="35"/>
       <c r="I119" s="37"/>
       <c r="J119" s="1"/>
     </row>
-    <row r="120" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="34"/>
       <c r="D120" s="35"/>
       <c r="E120" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F120" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G120" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G120" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H120" s="35"/>
       <c r="I120" s="37"/>
       <c r="J120" s="1"/>
     </row>
-    <row r="121" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D121" s="74"/>
-      <c r="E121" s="74"/>
-      <c r="F121" s="74"/>
-      <c r="G121" s="74"/>
-      <c r="H121" s="74"/>
-      <c r="I121" s="75"/>
+      <c r="C121" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D121" s="81"/>
+      <c r="E121" s="81"/>
+      <c r="F121" s="81"/>
+      <c r="G121" s="81"/>
+      <c r="H121" s="81"/>
+      <c r="I121" s="82"/>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="64">
         <v>14</v>
       </c>
       <c r="D122" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E122" s="66"/>
       <c r="F122" s="66"/>
       <c r="G122" s="67"/>
       <c r="H122" s="66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I122" s="68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="34"/>
       <c r="D123" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E123" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F123" s="35"/>
       <c r="G123" s="35"/>
@@ -11412,7 +11412,7 @@
       <c r="I123" s="37"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="34"/>
@@ -11424,16 +11424,16 @@
       <c r="I124" s="37"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="34"/>
       <c r="D125" s="35"/>
       <c r="E125" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F125" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G125" s="46">
         <v>5</v>
@@ -11442,16 +11442,16 @@
       <c r="I125" s="37"/>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="34"/>
       <c r="D126" s="35"/>
       <c r="E126" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F126" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G126" s="46">
         <v>2</v>
@@ -11460,16 +11460,16 @@
       <c r="I126" s="37"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="34"/>
       <c r="D127" s="35"/>
       <c r="E127" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F127" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G127" s="46">
         <v>6</v>
@@ -11478,65 +11478,65 @@
       <c r="I127" s="37"/>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
-      <c r="C128" s="73" t="s">
-        <v>103</v>
-      </c>
-      <c r="D128" s="74"/>
-      <c r="E128" s="74"/>
-      <c r="F128" s="74"/>
-      <c r="G128" s="74"/>
-      <c r="H128" s="74"/>
-      <c r="I128" s="75"/>
+      <c r="C128" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="D128" s="81"/>
+      <c r="E128" s="81"/>
+      <c r="F128" s="81"/>
+      <c r="G128" s="81"/>
+      <c r="H128" s="81"/>
+      <c r="I128" s="82"/>
       <c r="J128" s="1"/>
     </row>
-    <row r="129" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
-      <c r="C129" s="76" t="s">
-        <v>104</v>
-      </c>
-      <c r="D129" s="77"/>
-      <c r="E129" s="77"/>
-      <c r="F129" s="77"/>
-      <c r="G129" s="77"/>
+      <c r="C129" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="D129" s="79"/>
+      <c r="E129" s="79"/>
+      <c r="F129" s="79"/>
+      <c r="G129" s="79"/>
       <c r="H129" s="5"/>
       <c r="I129" s="29"/>
       <c r="J129" s="1"/>
     </row>
-    <row r="130" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="59">
         <v>15</v>
       </c>
       <c r="D130" s="60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E130" s="61"/>
       <c r="F130" s="61"/>
       <c r="G130" s="62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H130" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I130" s="63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J130" s="1"/>
     </row>
-    <row r="131" spans="1:10" ht="132" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" ht="132" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="34"/>
       <c r="D131" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E131" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F131" s="46"/>
       <c r="G131" s="46"/>
@@ -11544,7 +11544,7 @@
       <c r="I131" s="37"/>
       <c r="J131" s="1"/>
     </row>
-    <row r="132" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="34"/>
@@ -11556,16 +11556,16 @@
       <c r="I132" s="37"/>
       <c r="J132" s="1"/>
     </row>
-    <row r="133" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="34"/>
       <c r="D133" s="35"/>
       <c r="E133" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F133" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G133" s="46">
         <v>2</v>
@@ -11574,16 +11574,16 @@
       <c r="I133" s="37"/>
       <c r="J133" s="1"/>
     </row>
-    <row r="134" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="34"/>
       <c r="D134" s="35"/>
       <c r="E134" s="47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F134" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G134" s="46">
         <v>5</v>
@@ -11592,95 +11592,95 @@
       <c r="I134" s="37"/>
       <c r="J134" s="1"/>
     </row>
-    <row r="135" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="34"/>
       <c r="D135" s="35"/>
       <c r="E135" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F135" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G135" s="46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H135" s="35"/>
       <c r="I135" s="37"/>
       <c r="J135" s="1"/>
     </row>
-    <row r="136" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="34"/>
       <c r="D136" s="35"/>
       <c r="E136" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F136" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G136" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G136" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H136" s="35"/>
       <c r="I136" s="37"/>
       <c r="J136" s="1"/>
     </row>
-    <row r="137" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="34"/>
       <c r="D137" s="35"/>
       <c r="E137" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F137" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G137" s="46" t="s">
         <v>31</v>
-      </c>
-      <c r="G137" s="46" t="s">
-        <v>32</v>
       </c>
       <c r="H137" s="35"/>
       <c r="I137" s="37"/>
       <c r="J137" s="1"/>
     </row>
-    <row r="138" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="34"/>
       <c r="D138" s="35"/>
       <c r="E138" s="35"/>
-      <c r="F138" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="G138" s="72"/>
-      <c r="H138" s="72"/>
+      <c r="F138" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G138" s="75"/>
+      <c r="H138" s="75"/>
       <c r="I138" s="37"/>
       <c r="J138" s="1"/>
     </row>
-    <row r="139" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="34"/>
       <c r="D139" s="35"/>
       <c r="E139" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="F139" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G139" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="F139" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="G139" s="55" t="s">
+      <c r="H139" s="56" t="s">
         <v>112</v>
-      </c>
-      <c r="H139" s="56" t="s">
-        <v>113</v>
       </c>
       <c r="I139" s="37"/>
       <c r="J139" s="1"/>
     </row>
-    <row r="140" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="34"/>
@@ -11698,7 +11698,7 @@
       <c r="I140" s="37"/>
       <c r="J140" s="1"/>
     </row>
-    <row r="141" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="34"/>
@@ -11716,7 +11716,7 @@
       <c r="I141" s="37"/>
       <c r="J141" s="1"/>
     </row>
-    <row r="142" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="34"/>
@@ -11734,7 +11734,7 @@
       <c r="I142" s="37"/>
       <c r="J142" s="1"/>
     </row>
-    <row r="143" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="34"/>
@@ -11752,7 +11752,7 @@
       <c r="I143" s="37"/>
       <c r="J143" s="1"/>
     </row>
-    <row r="144" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="34"/>
@@ -11770,7 +11770,7 @@
       <c r="I144" s="37"/>
       <c r="J144" s="1"/>
     </row>
-    <row r="145" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="34"/>
@@ -11788,7 +11788,7 @@
       <c r="I145" s="37"/>
       <c r="J145" s="1"/>
     </row>
-    <row r="146" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="34"/>
@@ -11800,21 +11800,21 @@
       <c r="I146" s="37"/>
       <c r="J146" s="1"/>
     </row>
-    <row r="147" spans="1:10" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
-      <c r="C147" s="73" t="s">
-        <v>114</v>
-      </c>
-      <c r="D147" s="74"/>
-      <c r="E147" s="74"/>
-      <c r="F147" s="74"/>
-      <c r="G147" s="74"/>
-      <c r="H147" s="74"/>
-      <c r="I147" s="75"/>
+      <c r="C147" s="80" t="s">
+        <v>113</v>
+      </c>
+      <c r="D147" s="81"/>
+      <c r="E147" s="81"/>
+      <c r="F147" s="81"/>
+      <c r="G147" s="81"/>
+      <c r="H147" s="81"/>
+      <c r="I147" s="82"/>
       <c r="J147" s="1"/>
     </row>
-    <row r="148" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="43"/>
@@ -11826,31 +11826,42 @@
       <c r="I148" s="43"/>
       <c r="J148" s="1"/>
     </row>
-    <row r="149" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="35"/>
       <c r="D149" s="35"/>
       <c r="E149" s="35"/>
-      <c r="F149" s="71"/>
-      <c r="G149" s="71"/>
-      <c r="H149" s="71"/>
-      <c r="I149" s="71"/>
+      <c r="F149" s="97"/>
+      <c r="G149" s="97"/>
+      <c r="H149" s="97"/>
+      <c r="I149" s="97"/>
       <c r="J149" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C40:I40"/>
-    <mergeCell ref="C44:I44"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="H149:I149"/>
+    <mergeCell ref="F138:H138"/>
+    <mergeCell ref="C147:I147"/>
+    <mergeCell ref="C129:G129"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C121:I121"/>
+    <mergeCell ref="C113:I113"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="F109:H109"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="C88:I88"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="C102:I102"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="C75:I75"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="F71:G71"/>
     <mergeCell ref="C60:I60"/>
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="C45:G45"/>
@@ -11859,28 +11870,17 @@
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="G56:H56"/>
     <mergeCell ref="G57:H57"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="C75:I75"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="F109:H109"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="C88:I88"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="C102:I102"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C121:I121"/>
-    <mergeCell ref="C113:I113"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="F149:G149"/>
-    <mergeCell ref="H149:I149"/>
-    <mergeCell ref="F138:H138"/>
-    <mergeCell ref="C147:I147"/>
-    <mergeCell ref="C129:G129"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="C40:I40"/>
+    <mergeCell ref="C44:I44"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
